--- a/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-07-29).xlsx
+++ b/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-07-29).xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>291008487</v>
+        <v>4500000</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>291008487</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>317493140</v>
+        <v>19500000</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>1</v>
@@ -760,11 +760,15 @@
       <c r="H10" s="10" t="n">
         <v>19500000</v>
       </c>
-      <c r="I10" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>297993140</v>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -776,11 +780,15 @@
           <t>Badan Keuangan dan Aset Daerah</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>694885745</v>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -802,11 +810,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>694885745</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -819,10 +831,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>494143453</v>
+        <v>19928718</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>2</v>
@@ -836,11 +848,15 @@
       <c r="H12" s="10" t="n">
         <v>16692513</v>
       </c>
-      <c r="I12" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>474214735</v>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -853,10 +869,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>732115182</v>
+        <v>169489998</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>5</v>
@@ -870,11 +886,15 @@
       <c r="H13" s="6" t="n">
         <v>164526300</v>
       </c>
-      <c r="I13" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>562625184</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -887,10 +907,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>777986001</v>
+        <v>63250745</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>2</v>
@@ -904,11 +924,15 @@
       <c r="H14" s="10" t="n">
         <v>62335938</v>
       </c>
-      <c r="I14" s="8" t="n">
-        <v>123</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>714735256</v>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -921,10 +945,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>837899282</v>
+        <v>53461794</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>4</v>
@@ -938,11 +962,15 @@
       <c r="H15" s="6" t="n">
         <v>53392478</v>
       </c>
-      <c r="I15" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>784437488</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -955,10 +983,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>491911485</v>
+        <v>84108354</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>4</v>
@@ -972,11 +1000,15 @@
       <c r="H16" s="10" t="n">
         <v>78149208</v>
       </c>
-      <c r="I16" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>407803131</v>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
@@ -989,10 +1021,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>677290237</v>
+        <v>137583844</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>13</v>
@@ -1006,11 +1038,15 @@
       <c r="H17" s="6" t="n">
         <v>116218702</v>
       </c>
-      <c r="I17" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>539706393</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -1023,10 +1059,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>553370393</v>
+        <v>350423349</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>17</v>
@@ -1040,11 +1076,15 @@
       <c r="H18" s="10" t="n">
         <v>350174900</v>
       </c>
-      <c r="I18" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>202947044</v>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
@@ -1057,10 +1097,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>908204422</v>
+        <v>278259519</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>33</v>
@@ -1074,11 +1114,15 @@
       <c r="H19" s="6" t="n">
         <v>258444643</v>
       </c>
-      <c r="I19" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>629944903</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -1091,10 +1135,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>780728426</v>
+        <v>38508000</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>1</v>
@@ -1108,11 +1152,15 @@
       <c r="H20" s="10" t="n">
         <v>38508000</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>742220426</v>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
@@ -1125,10 +1173,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2090003236</v>
+        <v>1151124360</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>52</v>
@@ -1143,10 +1191,10 @@
         <v>1095681550.6</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>973878876</v>
+        <v>35000000</v>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -1159,10 +1207,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>444206345</v>
+        <v>32101092</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>5</v>
@@ -1176,11 +1224,15 @@
       <c r="H22" s="10" t="n">
         <v>29240607</v>
       </c>
-      <c r="I22" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>412105253</v>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -1193,10 +1245,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>342136823</v>
+        <v>30262050</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>4</v>
@@ -1211,10 +1263,10 @@
         <v>2476475</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>339474923</v>
+        <v>27600150</v>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -1227,10 +1279,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>794109241</v>
+        <v>81327566</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>4</v>
@@ -1244,11 +1296,15 @@
       <c r="H24" s="10" t="n">
         <v>75876500</v>
       </c>
-      <c r="I24" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>712781675</v>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -1261,10 +1317,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>304521329</v>
+        <v>98994684</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>4</v>
@@ -1278,11 +1334,15 @@
       <c r="H25" s="6" t="n">
         <v>51881289</v>
       </c>
-      <c r="I25" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>205526645</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -1295,10 +1355,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>234</v>
+        <v>45</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2238310494</v>
+        <v>520146698</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>30</v>
@@ -1313,10 +1373,10 @@
         <v>272586367</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>204</v>
+        <v>15</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>1963250696</v>
+        <v>245086900</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -1329,10 +1389,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>418455903</v>
+        <v>93366423</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>5</v>
@@ -1347,10 +1407,10 @@
         <v>48623430</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>369451185</v>
+        <v>44361705</v>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -1363,10 +1423,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>859678273</v>
+        <v>334343818</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>13</v>
@@ -1380,11 +1440,15 @@
       <c r="H28" s="10" t="n">
         <v>330804697</v>
       </c>
-      <c r="I28" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>525334455</v>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -1397,10 +1461,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>858385693</v>
+        <v>318496502</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>13</v>
@@ -1414,11 +1478,15 @@
       <c r="H29" s="6" t="n">
         <v>312310710</v>
       </c>
-      <c r="I29" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>539889191</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -1431,10 +1499,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>342405479</v>
+        <v>76153486</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>7</v>
@@ -1448,11 +1516,15 @@
       <c r="H30" s="10" t="n">
         <v>67861324</v>
       </c>
-      <c r="I30" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>266251993</v>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -1465,10 +1537,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1305525621</v>
+        <v>280944208</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>10</v>
@@ -1482,11 +1554,15 @@
       <c r="H31" s="6" t="n">
         <v>277956656</v>
       </c>
-      <c r="I31" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>1024581413</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -1499,10 +1575,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>851893680</v>
+        <v>502491122</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>21</v>
@@ -1516,11 +1592,15 @@
       <c r="H32" s="10" t="n">
         <v>437340098</v>
       </c>
-      <c r="I32" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>349402558</v>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -1533,10 +1613,10 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>744929925</v>
+        <v>69841346</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>13</v>
@@ -1550,11 +1630,15 @@
       <c r="H33" s="6" t="n">
         <v>63527950</v>
       </c>
-      <c r="I33" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>675088579</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
@@ -1567,10 +1651,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>550936395</v>
+        <v>73983300</v>
       </c>
       <c r="E34" s="8" t="n">
         <v>4</v>
@@ -1585,10 +1669,10 @@
         <v>20013167</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>530728095</v>
+        <v>53775000</v>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
@@ -1601,10 +1685,10 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>476139500</v>
+        <v>12917292</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>1</v>
@@ -1618,11 +1702,15 @@
       <c r="H35" s="6" t="n">
         <v>11908080</v>
       </c>
-      <c r="I35" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>463222208</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -1635,10 +1723,10 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>216696298</v>
+        <v>60000000</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>2</v>
@@ -1652,11 +1740,15 @@
       <c r="H36" s="10" t="n">
         <v>21674415</v>
       </c>
-      <c r="I36" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>156696298</v>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
@@ -1669,10 +1761,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>173</v>
+        <v>11</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1076116871</v>
+        <v>209482901</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>9</v>
@@ -1687,10 +1779,10 @@
         <v>111937628</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>961393970</v>
+        <v>94760000</v>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -1699,14 +1791,18 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>310252566</v>
+          <t>Kecamatan Kotawaringin Lama</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
@@ -1728,11 +1824,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>310252566</v>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -1741,40 +1841,32 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
+          <t>Kecamatan Kumai</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>382528466</v>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>186980127</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>152171825</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>145682100</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>382528466</v>
+        <v>34808302</v>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -1783,32 +1875,48 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>622521476</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>152171825</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>145682100</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>470349651</v>
+          <t>Kecamatan Pangkalan Banteng</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
@@ -1817,14 +1925,14 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>175284644</v>
+        <v>31600000</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
@@ -1847,10 +1955,10 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>175284644</v>
+        <v>31600000</v>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
@@ -1859,14 +1967,14 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>219851775</v>
+        <v>21000000</v>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
@@ -1889,10 +1997,10 @@
         </is>
       </c>
       <c r="I42" s="8" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>219851775</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="43" ht="45" customHeight="1">
@@ -1901,14 +2009,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>166377553</v>
+          <t>Puskesmas Natai Pelingkau</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -1930,11 +2042,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>166377553</v>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -1943,40 +2059,36 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
+          <t>Puskesmas Riam Durian</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>463616007</v>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>463616007</v>
+        <v>66380633</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>66380633</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>15724250</v>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -1985,40 +2097,36 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara</t>
+          <t>Rumah Sakit Kutaringin</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>51896600</v>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>51896600</v>
+        <v>35716900</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>35716900</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>26129400</v>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
@@ -2027,14 +2135,18 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>183754320</v>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
@@ -2056,11 +2168,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>183754320</v>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
@@ -2069,40 +2185,36 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya</t>
+          <t>Satuan Polisi Pamong Praja</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>489429711</v>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>489429711</v>
+        <v>119763291</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>119763291</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>118233150</v>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
@@ -2111,40 +2223,36 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama</t>
+          <t>Sekretariat DPRD</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>162372837</v>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>162372837</v>
+        <v>401182597</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>401182597</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>395443026</v>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
@@ -2153,746 +2261,68 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai</t>
+          <t>Sekretariat Daerah</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>397703689</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>397703689</v>
+        <v>183633343</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>183633343</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>160778238</v>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Kumpai Batu Atas</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>319912312</v>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>319912312</v>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>138079030</v>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>138079030</v>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>411198562</v>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>411198562</v>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>387164122</v>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>387164122</v>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="D54" s="10" t="n">
-        <v>289499767</v>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>289499767</v>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>240267455</v>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>240267455</v>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="D56" s="10" t="n">
-        <v>153251633</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F56" s="10" t="n">
-        <v>66380633</v>
-      </c>
-      <c r="G56" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H56" s="10" t="n">
-        <v>15724250</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>86871000</v>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>186180796</v>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>186180796</v>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D58" s="10" t="n">
-        <v>121367900</v>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>121367900</v>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>378945500</v>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>378945500</v>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D60" s="10" t="n">
-        <v>382606656</v>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>382606656</v>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>193865001</v>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>193865001</v>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="D62" s="10" t="n">
-        <v>345486342</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" s="10" t="n">
-        <v>35716900</v>
-      </c>
-      <c r="G62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>26129400</v>
-      </c>
-      <c r="I62" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>309769442</v>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>575029667</v>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>575029667</v>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D64" s="10" t="n">
-        <v>354293991</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F64" s="10" t="n">
-        <v>119763291</v>
-      </c>
-      <c r="G64" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" s="10" t="n">
-        <v>118233150</v>
-      </c>
-      <c r="I64" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="J64" s="10" t="n">
-        <v>234530700</v>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>1314919871</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>401182597</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>395443026</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>913737274</v>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n">
-        <v>147</v>
-      </c>
-      <c r="D66" s="10" t="n">
-        <v>1352438071</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F66" s="10" t="n">
-        <v>183633343</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="H66" s="10" t="n">
-        <v>160778238</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>127</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>1168804728</v>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C67" s="12" t="n">
-        <v>3878</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>32241583679</v>
-      </c>
-      <c r="E67" s="12" t="n">
+      <c r="C50" s="12" t="n">
+        <v>377</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>6211248060</v>
+      </c>
+      <c r="E50" s="12" t="n">
         <v>347</v>
       </c>
-      <c r="F67" s="13" t="n">
+      <c r="F50" s="13" t="n">
         <v>5618756003</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>347</v>
       </c>
-      <c r="H67" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>5251633789.6</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>3531</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>26622827676</v>
+      <c r="I50" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>592492057</v>
       </c>
     </row>
   </sheetData>
@@ -2924,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3194,10 +2624,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>259388320</v>
+        <v>59000000</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3240,10 +2670,10 @@
         </is>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>259388320</v>
+        <v>59000000</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
@@ -3256,10 +2686,10 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>513247490</v>
+        <v>190310330</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>2</v>
@@ -3289,11 +2719,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" s="10" t="n">
-        <v>322937160</v>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -3306,10 +2740,10 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>484082242</v>
+        <v>168902040</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>1</v>
@@ -3339,11 +2773,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>315180202</v>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -3356,10 +2794,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>869448547</v>
+        <v>439139830</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>4</v>
@@ -3385,11 +2823,15 @@
       <c r="L12" s="10" t="n">
         <v>57714450</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N12" s="10" t="n">
-        <v>430308717</v>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -3402,10 +2844,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1559854479</v>
+        <v>817935443</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>5</v>
@@ -3436,10 +2878,10 @@
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>1049541276</v>
+        <v>307622240</v>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -3505,11 +2947,15 @@
           <t>Dinas Kepemudaan dan Olahraga</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>957216782</v>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -3551,11 +2997,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>957216782</v>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -3568,10 +3018,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>266301572</v>
+        <v>54773006</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>1</v>
@@ -3601,11 +3051,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>211528566</v>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
@@ -3618,10 +3072,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1566751699</v>
+        <v>1170042538</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>10</v>
@@ -3648,10 +3102,10 @@
         <v>237557765</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>471393957</v>
+        <v>74684796</v>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -3664,10 +3118,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>1109929988</v>
+        <v>873381088</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>11</v>
@@ -3693,11 +3147,15 @@
       <c r="L18" s="10" t="n">
         <v>55664280</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="10" t="n">
-        <v>236548900</v>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
@@ -3710,10 +3168,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1888168641</v>
+        <v>905090000</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>6</v>
@@ -3739,11 +3197,15 @@
       <c r="L19" s="6" t="n">
         <v>194832750</v>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>983078641</v>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -3756,10 +3218,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1467806996</v>
+        <v>429952000</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>3</v>
@@ -3789,11 +3251,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" s="10" t="n">
-        <v>1037854996</v>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
@@ -3806,10 +3272,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>19684340479</v>
+        <v>17216344778</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>122</v>
@@ -3835,11 +3301,15 @@
       <c r="L21" s="6" t="n">
         <v>72965295</v>
       </c>
-      <c r="M21" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>2467995701</v>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -3852,10 +3322,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>376694000</v>
+        <v>288750000</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>2</v>
@@ -3885,11 +3355,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="10" t="n">
-        <v>87944000</v>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -3902,10 +3376,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>405798874</v>
+        <v>66310000</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>1</v>
@@ -3935,11 +3409,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>339488874</v>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -3952,10 +3430,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>610038436</v>
+        <v>146351500</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>2</v>
@@ -3985,11 +3463,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" s="10" t="n">
-        <v>463686936</v>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -4056,10 +3538,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>6408513766</v>
+        <v>3621914097</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>24</v>
@@ -4090,10 +3572,10 @@
         </is>
       </c>
       <c r="M26" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>3430812569</v>
+        <v>644212900</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -4106,10 +3588,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1177904322</v>
+        <v>913021368</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>7</v>
@@ -4139,11 +3621,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>264882954</v>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -4156,10 +3642,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>5044708697</v>
+        <v>3344224943</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>24</v>
@@ -4190,10 +3676,10 @@
         </is>
       </c>
       <c r="M28" s="8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>1822466094</v>
+        <v>121982340</v>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -4206,10 +3692,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2784104510</v>
+        <v>743457601</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>7</v>
@@ -4235,11 +3721,15 @@
       <c r="L29" s="6" t="n">
         <v>50500763</v>
       </c>
-      <c r="M29" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>2040646909</v>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -4251,11 +3741,15 @@
           <t>Dinas Perpustakaan dan Kearsipan</t>
         </is>
       </c>
-      <c r="C30" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>190561024</v>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
@@ -4297,11 +3791,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" s="10" t="n">
-        <v>190561024</v>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -4314,10 +3812,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>4842583639</v>
+        <v>2428743641</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>20</v>
@@ -4343,11 +3841,15 @@
       <c r="L31" s="6" t="n">
         <v>94888350</v>
       </c>
-      <c r="M31" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>2413839998</v>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -4360,10 +3862,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>24100076698</v>
+        <v>18681965778</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>132</v>
@@ -4394,10 +3896,10 @@
         </is>
       </c>
       <c r="M32" s="8" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>6764951620</v>
+        <v>1346840700</v>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -4409,11 +3911,15 @@
           <t>Dinas Sosial</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>1113387305</v>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -4455,11 +3961,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M33" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v>1113387305</v>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
@@ -4471,11 +3981,15 @@
           <t>Dinas Tenaga Kerja dan Transmigrasi</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>346039368</v>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
@@ -4517,11 +4031,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" s="10" t="n">
-        <v>346039368</v>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
@@ -4533,11 +4051,15 @@
           <t>Inspektorat Daerah</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>470786500</v>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -4579,11 +4101,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M35" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N35" s="6" t="n">
-        <v>470786500</v>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -4596,10 +4122,10 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>523391100</v>
+        <v>293964700</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>2</v>
@@ -4630,10 +4156,10 @@
         </is>
       </c>
       <c r="M36" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>301408750</v>
+        <v>71982350</v>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
@@ -4646,10 +4172,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>835283701</v>
+        <v>471330601</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>6</v>
@@ -4679,11 +4205,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M37" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N37" s="6" t="n">
-        <v>363953100</v>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -4692,14 +4222,18 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>154997000</v>
+          <t>Kecamatan Kotawaringin Lama</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
@@ -4741,11 +4275,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" s="10" t="n">
-        <v>154997000</v>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -4754,14 +4292,14 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
+          <t>Kecamatan Kumai</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>124841500</v>
+        <v>133439000</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -4807,7 +4345,7 @@
         <v>2</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>124841500</v>
+        <v>133439000</v>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -4816,44 +4354,32 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>320725524</v>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>71700000</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>71700000</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>71700000</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>71700000</v>
       </c>
       <c r="K40" s="11" t="inlineStr">
         <is>
@@ -4865,11 +4391,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M40" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N40" s="10" t="n">
-        <v>320725524</v>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
@@ -4878,32 +4408,32 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>137310832</v>
+        <v>239852458</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>71700000</v>
+        <v>239852458</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>71700000</v>
+        <v>65401200</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>71700000</v>
+        <v>65401200</v>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
@@ -4915,11 +4445,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" s="6" t="n">
-        <v>65610832</v>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
@@ -4928,7 +4462,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -4998,32 +4532,32 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
+          <t>Puskesmas Natai Pelingkau</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>302731124</v>
+        <v>348491630</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>239852458</v>
+        <v>153891630</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>65401200</v>
+        <v>53835000</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>65401200</v>
+        <v>53835000</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
@@ -5039,7 +4573,7 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>62878666</v>
+        <v>194600000</v>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -5048,14 +4582,18 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>305850296</v>
+          <t>Puskesmas Riam Durian</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
@@ -5097,11 +4635,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M44" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N44" s="10" t="n">
-        <v>305850296</v>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -5110,44 +4652,32 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara</t>
+          <t>Rumah Sakit Kutaringin</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>212926585</v>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>146817603</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>146817603</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>43541637</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>43541637</v>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
@@ -5159,11 +4689,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>212926585</v>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
@@ -5172,44 +4706,32 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya</t>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>154700000</v>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>50400000</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>50400000</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>49950000</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>49950000</v>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
@@ -5221,11 +4743,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" s="10" t="n">
-        <v>154700000</v>
+      <c r="M46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
@@ -5234,14 +4760,18 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>397980729</v>
+          <t>Satuan Polisi Pamong Praja</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -5283,11 +4813,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M47" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N47" s="6" t="n">
-        <v>397980729</v>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
@@ -5296,44 +4830,32 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama</t>
+          <t>Sekretariat DPRD</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>50400000</v>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1435364766</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>1285364766</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>1282534627</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>1226738257</v>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
@@ -5349,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>50400000</v>
+        <v>150000000</v>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
@@ -5358,44 +4880,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai</t>
+          <t>Sekretariat Daerah</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>749487047</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D49" s="6" t="n">
-        <v>494958640</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F49" s="6" t="n">
+        <v>573698247</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>560374825</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>486004825</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
@@ -5408,1064 +4918,54 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>494958640</v>
+        <v>175788800</v>
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Kumpai Batu Atas</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>189350000</v>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N50" s="10" t="n">
-        <v>189350000</v>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>235342500</v>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" s="6" t="n">
-        <v>235342500</v>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>141393225</v>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M52" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" s="10" t="n">
-        <v>141393225</v>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>348491630</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>153891630</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>53835000</v>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>53835000</v>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N53" s="6" t="n">
-        <v>194600000</v>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>189000000</v>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>143150000</v>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>143150000</v>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="10" t="n">
-        <v>149292000</v>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" s="10" t="n">
-        <v>149292000</v>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>275450000</v>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N59" s="6" t="n">
-        <v>275450000</v>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="10" t="n">
-        <v>66272893</v>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="10" t="n">
-        <v>66272893</v>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>156525300</v>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>156525300</v>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D62" s="10" t="n">
-        <v>647501699</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="10" t="n">
-        <v>146817603</v>
-      </c>
-      <c r="G62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>43541637</v>
-      </c>
-      <c r="I62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>43541637</v>
-      </c>
-      <c r="K62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N62" s="10" t="n">
-        <v>500684096</v>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>3441387498</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>50400000</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>49950000</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>49950000</v>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="N63" s="6" t="n">
-        <v>3390987498</v>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D64" s="10" t="n">
-        <v>463002876</v>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N64" s="10" t="n">
-        <v>463002876</v>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>2559430816</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>1285364766</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>1282534627</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>1226738257</v>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N65" s="6" t="n">
-        <v>1274066050</v>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="D66" s="10" t="n">
-        <v>2995755132</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F66" s="10" t="n">
-        <v>573698247</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H66" s="10" t="n">
-        <v>560374825</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>486004825</v>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="N66" s="10" t="n">
-        <v>2422056885</v>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C67" s="12" t="n">
-        <v>798</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>94774837904</v>
-      </c>
-      <c r="E67" s="12" t="n">
+      <c r="C50" s="12" t="n">
+        <v>442</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>56760118716</v>
+      </c>
+      <c r="E50" s="12" t="n">
         <v>417</v>
       </c>
-      <c r="F67" s="13" t="n">
+      <c r="F50" s="13" t="n">
         <v>53479965590</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>417</v>
       </c>
-      <c r="H67" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>51736639593.4</v>
       </c>
-      <c r="I67" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="J67" s="13" t="n">
+      <c r="J50" s="13" t="n">
         <v>24211949095</v>
       </c>
-      <c r="K67" s="12" t="n">
+      <c r="K50" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L67" s="13" t="n">
+      <c r="L50" s="13" t="n">
         <v>764123653</v>
       </c>
-      <c r="M67" s="12" t="n">
-        <v>381</v>
-      </c>
-      <c r="N67" s="13" t="n">
-        <v>41294872314</v>
+      <c r="M50" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>3280153126</v>
       </c>
     </row>
   </sheetData>
@@ -6497,7 +4997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6898,11 +5398,15 @@
           <t>Badan Keuangan dan Aset Daerah</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>206878992</v>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -6944,11 +5448,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>206878992</v>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -7031,10 +5539,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1344967600</v>
+        <v>1128517600</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>1</v>
@@ -7065,10 +5573,10 @@
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>1128517600</v>
+        <v>912067600</v>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -7080,11 +5588,15 @@
           <t>Badan Perencanaan Pembangunan, Riset dan Inovasi Daerah</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>217952667</v>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
@@ -7126,11 +5638,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="10" t="n">
-        <v>217952667</v>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -7142,11 +5658,15 @@
           <t>Dinas Kepemudaan dan Olahraga</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>658884360</v>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -7188,11 +5708,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>658884360</v>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -7255,10 +5779,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>50117240767</v>
+        <v>49112440318</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>32</v>
@@ -7284,11 +5808,15 @@
       <c r="L17" s="6" t="n">
         <v>1101458974</v>
       </c>
-      <c r="M17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>1004800449</v>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -7371,10 +5899,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>6129521900</v>
+        <v>3459514800</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>4</v>
@@ -7404,11 +5932,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>2670007100</v>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -7475,10 +6007,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>35948239265</v>
+        <v>33346991733</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>42</v>
@@ -7508,11 +6040,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M21" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>2601247532</v>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -7525,10 +6061,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>1366776000</v>
+        <v>1086690000</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>2</v>
@@ -7558,11 +6094,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="10" t="n">
-        <v>280086000</v>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -7574,11 +6114,15 @@
           <t>Dinas Pemberdayaan Masyarakat dan Desa</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>914760000</v>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -7620,11 +6164,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>914760000</v>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -7636,11 +6184,15 @@
           <t>Dinas Pemberdayaan Perempuan dan Perlindungan Anak, Pengendalian Penduduk dan Keluarga Berencana</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>777000000</v>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
@@ -7682,11 +6234,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" s="10" t="n">
-        <v>777000000</v>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -7698,11 +6254,15 @@
           <t>Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>205076880</v>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -7744,11 +6304,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>205076880</v>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -7761,10 +6325,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2966457340</v>
+        <v>1969342000</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>3</v>
@@ -7795,10 +6359,10 @@
         </is>
       </c>
       <c r="M26" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>2253119340</v>
+        <v>1256004000</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -7811,10 +6375,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>729033456</v>
+        <v>201600000</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>1</v>
@@ -7844,11 +6408,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>527433456</v>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -7861,10 +6429,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>2208956507</v>
+        <v>1062414494</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>3</v>
@@ -7895,10 +6463,10 @@
         </is>
       </c>
       <c r="M28" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>1376538977</v>
+        <v>229996964</v>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -7911,10 +6479,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>5338130896</v>
+        <v>4037584000</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>4</v>
@@ -7940,11 +6508,15 @@
       <c r="L29" s="6" t="n">
         <v>436796630</v>
       </c>
-      <c r="M29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>1300546896</v>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -8027,10 +6599,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3813601480</v>
+        <v>2620841480</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>7</v>
@@ -8061,10 +6633,10 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>1437760000</v>
+        <v>245000000</v>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -8077,10 +6649,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3639664785</v>
+        <v>1106740800</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>2</v>
@@ -8111,10 +6683,10 @@
         </is>
       </c>
       <c r="M32" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>3093962385</v>
+        <v>561038400</v>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -8405,18 +6977,14 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Kecamatan Kotawaringin Lama</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>440899992</v>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
@@ -8458,15 +7026,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="10" t="n">
+        <v>440899992</v>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -8475,14 +7039,18 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>440899992</v>
+          <t>Kecamatan Kumai</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -8524,11 +7092,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" s="6" t="n">
-        <v>440899992</v>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -8537,7 +7109,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -8607,7 +7179,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -8677,7 +7249,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -8747,14 +7319,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>1937370950</v>
+          <t>Puskesmas Natai Pelingkau</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -8796,11 +7372,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N43" s="6" t="n">
-        <v>1937370950</v>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -8809,14 +7389,18 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>1032445697</v>
+          <t>Puskesmas Riam Durian</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
@@ -8858,11 +7442,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" s="10" t="n">
-        <v>1032445697</v>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -8871,14 +7459,18 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>456516000</v>
+          <t>Rumah Sakit Kutaringin</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -8920,11 +7512,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>456516000</v>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
@@ -8933,58 +7529,38 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>7812519000</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>7812519000</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>2779934202</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>2779934202</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>64551162</v>
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
@@ -9003,7 +7579,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya</t>
+          <t>Satuan Polisi Pamong Praja</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -9073,48 +7649,32 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Sekretariat DPRD</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>218268000</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>218268000</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>185076000</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>185076000</v>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
@@ -9143,44 +7703,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai</t>
+          <t>Sekretariat Daerah</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>223700000</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2944207800</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>2944207800</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>2058441500</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>2058441500</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
@@ -9192,1173 +7740,59 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="6" t="n">
-        <v>223700000</v>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Kumpai Batu Atas</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL KESELURUHAN</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>117525967542</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>121</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>112850154586</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>121</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>55094743286</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>53004449286</v>
+      </c>
+      <c r="K50" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="D63" s="6" t="n">
-        <v>15827645837</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>7812519000</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>2779934202</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>2779934202</v>
-      </c>
-      <c r="K63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" s="6" t="n">
-        <v>64551162</v>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="N63" s="6" t="n">
-        <v>8015126837</v>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="10" t="n">
-        <v>211404000</v>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N64" s="10" t="n">
-        <v>211404000</v>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>5031291001</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>218268000</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>185076000</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>185076000</v>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N65" s="6" t="n">
-        <v>4813023001</v>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n">
+      <c r="L50" s="13" t="n">
+        <v>2094471498</v>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="D66" s="10" t="n">
-        <v>7626623356</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F66" s="10" t="n">
-        <v>2944207800</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H66" s="10" t="n">
-        <v>2058441500</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>2058441500</v>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="N66" s="10" t="n">
-        <v>4682415556</v>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL KESELURUHAN</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="n">
-        <v>212</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>156348435253</v>
-      </c>
-      <c r="E67" s="12" t="n">
-        <v>121</v>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>112850154586</v>
-      </c>
-      <c r="G67" s="12" t="n">
-        <v>121</v>
-      </c>
-      <c r="H67" s="13" t="n">
-        <v>55094743286</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>53004449286</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L67" s="13" t="n">
-        <v>2094471498</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="N67" s="13" t="n">
-        <v>43498280667</v>
+      <c r="N50" s="13" t="n">
+        <v>4675812956</v>
       </c>
     </row>
   </sheetData>
@@ -10390,7 +7824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11864,10 +9298,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8328788319</v>
+        <v>5040000000</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>1</v>
@@ -11897,11 +9331,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>3288788319</v>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -12107,11 +9545,15 @@
           <t>Dinas Pertanian</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>2509875000</v>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -12153,11 +9595,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>2509875000</v>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -12586,7 +10032,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara</t>
+          <t>Kecamatan Kotawaringin Lama</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -12656,7 +10102,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
+          <t>Kecamatan Kumai</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -12726,7 +10172,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -12796,7 +10242,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -12866,7 +10312,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -12936,7 +10382,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
+          <t>Puskesmas Natai Pelingkau</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -13006,7 +10452,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
+          <t>Puskesmas Riam Durian</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -13076,7 +10522,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara</t>
+          <t>Rumah Sakit Kutaringin</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -13146,48 +10592,32 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>73360000000</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>73360000000</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>8116023274</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>8116023274</v>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
@@ -13216,7 +10646,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya</t>
+          <t>Satuan Polisi Pamong Praja</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -13286,7 +10716,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama</t>
+          <t>Sekretariat DPRD</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -13356,7 +10786,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai</t>
+          <t>Sekretariat Daerah</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -13421,1221 +10851,51 @@
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Kumpai Batu Atas</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>135106211738</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>73360000000</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>8116023274</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>8116023274</v>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M63" s="4" t="n">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL KESELURUHAN</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>187157560800</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>137115370800</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>71014601008.97</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>71014601008.97</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N63" s="6" t="n">
-        <v>61746211738</v>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL KESELURUHAN</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>254702435857</v>
-      </c>
-      <c r="E67" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>137115370800</v>
-      </c>
-      <c r="G67" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="H67" s="13" t="n">
-        <v>71014601008.97</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>71014601008.97</v>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="N67" s="13" t="n">
-        <v>117587065057</v>
+      <c r="N50" s="13" t="n">
+        <v>50042190000</v>
       </c>
     </row>
   </sheetData>

--- a/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-07-29).xlsx
+++ b/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-07-29).xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4500000</v>
+        <v>291008487</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>4500000</v>
+        <v>291008487</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>19500000</v>
+        <v>317493140</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>1</v>
@@ -760,15 +760,11 @@
       <c r="H10" s="10" t="n">
         <v>19500000</v>
       </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>297993140</v>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -780,15 +776,11 @@
           <t>Badan Keuangan dan Aset Daerah</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>694885745</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -810,15 +802,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>694885745</v>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -831,10 +819,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>19928718</v>
+        <v>494143453</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>2</v>
@@ -848,15 +836,11 @@
       <c r="H12" s="10" t="n">
         <v>16692513</v>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>474214735</v>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -869,10 +853,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>169489998</v>
+        <v>732115182</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>5</v>
@@ -886,15 +870,11 @@
       <c r="H13" s="6" t="n">
         <v>164526300</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>562625184</v>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -907,10 +887,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>63250745</v>
+        <v>777986001</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>2</v>
@@ -924,15 +904,11 @@
       <c r="H14" s="10" t="n">
         <v>62335938</v>
       </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>714735256</v>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -945,10 +921,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>53461794</v>
+        <v>837899282</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>4</v>
@@ -962,15 +938,11 @@
       <c r="H15" s="6" t="n">
         <v>53392478</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>784437488</v>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -983,10 +955,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>84108354</v>
+        <v>491911485</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>4</v>
@@ -1000,15 +972,11 @@
       <c r="H16" s="10" t="n">
         <v>78149208</v>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>407803131</v>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
@@ -1021,10 +989,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>137583844</v>
+        <v>677290237</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>13</v>
@@ -1038,15 +1006,11 @@
       <c r="H17" s="6" t="n">
         <v>116218702</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>539706393</v>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -1059,10 +1023,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>350423349</v>
+        <v>553370393</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>17</v>
@@ -1076,15 +1040,11 @@
       <c r="H18" s="10" t="n">
         <v>350174900</v>
       </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>202947044</v>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
@@ -1097,10 +1057,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>278259519</v>
+        <v>908204422</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>33</v>
@@ -1114,15 +1074,11 @@
       <c r="H19" s="6" t="n">
         <v>258444643</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>629944903</v>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -1135,10 +1091,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>38508000</v>
+        <v>780728426</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>1</v>
@@ -1152,15 +1108,11 @@
       <c r="H20" s="10" t="n">
         <v>38508000</v>
       </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>742220426</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
@@ -1173,10 +1125,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1151124360</v>
+        <v>2090003236</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>52</v>
@@ -1191,10 +1143,10 @@
         <v>1095681550.6</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>35000000</v>
+        <v>973878876</v>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -1207,10 +1159,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>32101092</v>
+        <v>444206345</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>5</v>
@@ -1224,15 +1176,11 @@
       <c r="H22" s="10" t="n">
         <v>29240607</v>
       </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>412105253</v>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -1245,10 +1193,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>30262050</v>
+        <v>342136823</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>4</v>
@@ -1263,10 +1211,10 @@
         <v>2476475</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>27600150</v>
+        <v>339474923</v>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -1279,10 +1227,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>81327566</v>
+        <v>794109241</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>4</v>
@@ -1296,15 +1244,11 @@
       <c r="H24" s="10" t="n">
         <v>75876500</v>
       </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>712781675</v>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -1317,10 +1261,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>98994684</v>
+        <v>304521329</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>4</v>
@@ -1334,15 +1278,11 @@
       <c r="H25" s="6" t="n">
         <v>51881289</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>205526645</v>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -1355,10 +1295,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>45</v>
+        <v>234</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>520146698</v>
+        <v>2238310494</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>30</v>
@@ -1373,10 +1313,10 @@
         <v>272586367</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>245086900</v>
+        <v>1963250696</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -1389,10 +1329,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>93366423</v>
+        <v>418455903</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>5</v>
@@ -1407,10 +1347,10 @@
         <v>48623430</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>44361705</v>
+        <v>369451185</v>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -1423,10 +1363,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>334343818</v>
+        <v>859678273</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>13</v>
@@ -1440,15 +1380,11 @@
       <c r="H28" s="10" t="n">
         <v>330804697</v>
       </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>525334455</v>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -1461,10 +1397,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>318496502</v>
+        <v>858385693</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>13</v>
@@ -1478,15 +1414,11 @@
       <c r="H29" s="6" t="n">
         <v>312310710</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>539889191</v>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -1499,10 +1431,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>76153486</v>
+        <v>342405479</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>7</v>
@@ -1516,15 +1448,11 @@
       <c r="H30" s="10" t="n">
         <v>67861324</v>
       </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>266251993</v>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -1537,10 +1465,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>280944208</v>
+        <v>1305525621</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>10</v>
@@ -1554,15 +1482,11 @@
       <c r="H31" s="6" t="n">
         <v>277956656</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>1024581413</v>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -1575,10 +1499,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>502491122</v>
+        <v>851893680</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>21</v>
@@ -1592,15 +1516,11 @@
       <c r="H32" s="10" t="n">
         <v>437340098</v>
       </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>349402558</v>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -1613,10 +1533,10 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>69841346</v>
+        <v>744929925</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>13</v>
@@ -1630,15 +1550,11 @@
       <c r="H33" s="6" t="n">
         <v>63527950</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>675088579</v>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
@@ -1651,10 +1567,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>73983300</v>
+        <v>550936395</v>
       </c>
       <c r="E34" s="8" t="n">
         <v>4</v>
@@ -1669,10 +1585,10 @@
         <v>20013167</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>53775000</v>
+        <v>530728095</v>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
@@ -1685,10 +1601,10 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>12917292</v>
+        <v>476139500</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>1</v>
@@ -1702,15 +1618,11 @@
       <c r="H35" s="6" t="n">
         <v>11908080</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>463222208</v>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -1723,10 +1635,10 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>60000000</v>
+        <v>216696298</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>2</v>
@@ -1740,15 +1652,11 @@
       <c r="H36" s="10" t="n">
         <v>21674415</v>
       </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>156696298</v>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
@@ -1761,10 +1669,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>209482901</v>
+        <v>1076116871</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>9</v>
@@ -1779,10 +1687,10 @@
         <v>111937628</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>94760000</v>
+        <v>961393970</v>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -1791,18 +1699,14 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Kecamatan Arut Utara</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>310252566</v>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
@@ -1824,15 +1728,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>310252566</v>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -1841,32 +1741,40 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
+          <t>Kecamatan Kotawaringin Lama</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>186980127</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>152171825</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>145682100</v>
+        <v>382528466</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>34808302</v>
+        <v>382528466</v>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -1875,48 +1783,32 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Kecamatan Kumai</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>622521476</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>152171825</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>145682100</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>470349651</v>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
@@ -1925,14 +1817,14 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>31600000</v>
+        <v>175284644</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
@@ -1955,10 +1847,10 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>31600000</v>
+        <v>175284644</v>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
@@ -1967,14 +1859,14 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
+          <t>Kecamatan Pangkalan Lada</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>21000000</v>
+        <v>219851775</v>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
@@ -1997,10 +1889,10 @@
         </is>
       </c>
       <c r="I42" s="8" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>21000000</v>
+        <v>219851775</v>
       </c>
     </row>
     <row r="43" ht="45" customHeight="1">
@@ -2009,18 +1901,14 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Laboratorium Kesehatan Daerah</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>166377553</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -2042,15 +1930,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>166377553</v>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -2059,36 +1943,40 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Riam Durian</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>66380633</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>66380633</v>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H44" s="10" t="n">
-        <v>15724250</v>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>463616007</v>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>463616007</v>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -2097,36 +1985,40 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Rumah Sakit Kutaringin</t>
+          <t>Puskesmas Arut Utara</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>35716900</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>35716900</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>26129400</v>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>51896600</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>51896600</v>
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
@@ -2135,18 +2027,14 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Puskesmas Ipuh Bangun Jaya</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>183754320</v>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
@@ -2168,15 +2056,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>183754320</v>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
@@ -2185,36 +2069,40 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Satuan Polisi Pamong Praja</t>
+          <t>Puskesmas Karang Mulya</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>119763291</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>119763291</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>118233150</v>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>489429711</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>489429711</v>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
@@ -2223,36 +2111,40 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Sekretariat DPRD</t>
+          <t>Puskesmas Kotawaringin Lama</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>401182597</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="F48" s="10" t="n">
-        <v>401182597</v>
-      </c>
-      <c r="G48" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="H48" s="10" t="n">
-        <v>395443026</v>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>162372837</v>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>162372837</v>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
@@ -2261,68 +2153,746 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
+          <t>Puskesmas Kumai</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>397703689</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>397703689</v>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Kumpai Batu Atas</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>319912312</v>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>319912312</v>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Madurejo</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>138079030</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>138079030</v>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Mendawai</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>411198562</v>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>411198562</v>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Natai Pelingkau</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>387164122</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>387164122</v>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Pandu Sanjaya</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>289499767</v>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>289499767</v>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Pangkalan Lada</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>240267455</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>240267455</v>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Riam Durian</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>153251633</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>66380633</v>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>15724250</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>86871000</v>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Runtu</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>186180796</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>186180796</v>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Sambi</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>121367900</v>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>121367900</v>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Semanggang</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>378945500</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>378945500</v>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Sungai Rangit</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D60" s="10" t="n">
+        <v>382606656</v>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>382606656</v>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Teluk Bogam</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>193865001</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>193865001</v>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Kutaringin</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>345486342</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>35716900</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>26129400</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>309769442</v>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>575029667</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>575029667</v>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Satuan Polisi Pamong Praja</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>354293991</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>119763291</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" s="10" t="n">
+        <v>118233150</v>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>234530700</v>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Sekretariat DPRD</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>1314919871</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>401182597</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>395443026</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>913737274</v>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
           <t>Sekretariat Daerah</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C66" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="D66" s="10" t="n">
+        <v>1352438071</v>
+      </c>
+      <c r="E66" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="F66" s="10" t="n">
         <v>183633343</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="G66" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F49" s="6" t="n">
-        <v>183633343</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H49" s="6" t="n">
+      <c r="H66" s="10" t="n">
         <v>160778238</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="I66" s="8" t="n">
+        <v>127</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>1168804728</v>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
-        <v>377</v>
-      </c>
-      <c r="D50" s="13" t="n">
-        <v>6211248060</v>
-      </c>
-      <c r="E50" s="12" t="n">
+      <c r="C67" s="12" t="n">
+        <v>3878</v>
+      </c>
+      <c r="D67" s="13" t="n">
+        <v>32241583679</v>
+      </c>
+      <c r="E67" s="12" t="n">
         <v>347</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="F67" s="13" t="n">
         <v>5618756003</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>347</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="H67" s="13" t="n">
         <v>5251633789.6</v>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>592492057</v>
+      <c r="I67" s="12" t="n">
+        <v>3531</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>26622827676</v>
       </c>
     </row>
   </sheetData>
@@ -2354,7 +2924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2624,10 +3194,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>59000000</v>
+        <v>259388320</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -2670,10 +3240,10 @@
         </is>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>59000000</v>
+        <v>259388320</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
@@ -2686,10 +3256,10 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>190310330</v>
+        <v>513247490</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>2</v>
@@ -2719,15 +3289,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>322937160</v>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -2740,10 +3306,10 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>168902040</v>
+        <v>484082242</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>1</v>
@@ -2773,15 +3339,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>315180202</v>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -2794,10 +3356,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>439139830</v>
+        <v>869448547</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>4</v>
@@ -2823,15 +3385,11 @@
       <c r="L12" s="10" t="n">
         <v>57714450</v>
       </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>430308717</v>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -2844,10 +3402,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>817935443</v>
+        <v>1559854479</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>5</v>
@@ -2878,10 +3436,10 @@
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>307622240</v>
+        <v>1049541276</v>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -2947,15 +3505,11 @@
           <t>Dinas Kepemudaan dan Olahraga</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>957216782</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -2997,15 +3551,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>957216782</v>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -3018,10 +3568,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>54773006</v>
+        <v>266301572</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>1</v>
@@ -3051,15 +3601,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>211528566</v>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
@@ -3072,10 +3618,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1170042538</v>
+        <v>1566751699</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>10</v>
@@ -3102,10 +3648,10 @@
         <v>237557765</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>74684796</v>
+        <v>471393957</v>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -3118,10 +3664,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>873381088</v>
+        <v>1109929988</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>11</v>
@@ -3147,15 +3693,11 @@
       <c r="L18" s="10" t="n">
         <v>55664280</v>
       </c>
-      <c r="M18" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M18" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>236548900</v>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
@@ -3168,10 +3710,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>905090000</v>
+        <v>1888168641</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>6</v>
@@ -3197,15 +3739,11 @@
       <c r="L19" s="6" t="n">
         <v>194832750</v>
       </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>983078641</v>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -3218,10 +3756,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>429952000</v>
+        <v>1467806996</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>3</v>
@@ -3251,15 +3789,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M20" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>1037854996</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
@@ -3272,10 +3806,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>17216344778</v>
+        <v>19684340479</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>122</v>
@@ -3301,15 +3835,11 @@
       <c r="L21" s="6" t="n">
         <v>72965295</v>
       </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M21" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>2467995701</v>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -3322,10 +3852,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>288750000</v>
+        <v>376694000</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>2</v>
@@ -3355,15 +3885,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>87944000</v>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -3376,10 +3902,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>66310000</v>
+        <v>405798874</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>1</v>
@@ -3409,15 +3935,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M23" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>339488874</v>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -3430,10 +3952,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>146351500</v>
+        <v>610038436</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>2</v>
@@ -3463,15 +3985,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>463686936</v>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -3538,10 +4056,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>3621914097</v>
+        <v>6408513766</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>24</v>
@@ -3572,10 +4090,10 @@
         </is>
       </c>
       <c r="M26" s="8" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>644212900</v>
+        <v>3430812569</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -3588,10 +4106,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>913021368</v>
+        <v>1177904322</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>7</v>
@@ -3621,15 +4139,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>264882954</v>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -3642,10 +4156,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>3344224943</v>
+        <v>5044708697</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>24</v>
@@ -3676,10 +4190,10 @@
         </is>
       </c>
       <c r="M28" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>121982340</v>
+        <v>1822466094</v>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -3692,10 +4206,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>743457601</v>
+        <v>2784104510</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>7</v>
@@ -3721,15 +4235,11 @@
       <c r="L29" s="6" t="n">
         <v>50500763</v>
       </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M29" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>2040646909</v>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -3741,15 +4251,11 @@
           <t>Dinas Perpustakaan dan Kearsipan</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C30" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>190561024</v>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
@@ -3791,15 +4297,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M30" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v>190561024</v>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -3812,10 +4314,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2428743641</v>
+        <v>4842583639</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>20</v>
@@ -3841,15 +4343,11 @@
       <c r="L31" s="6" t="n">
         <v>94888350</v>
       </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M31" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>2413839998</v>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -3862,10 +4360,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>18681965778</v>
+        <v>24100076698</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>132</v>
@@ -3896,10 +4394,10 @@
         </is>
       </c>
       <c r="M32" s="8" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>1346840700</v>
+        <v>6764951620</v>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -3911,15 +4409,11 @@
           <t>Dinas Sosial</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C33" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1113387305</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -3961,15 +4455,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M33" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>1113387305</v>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
@@ -3981,15 +4471,11 @@
           <t>Dinas Tenaga Kerja dan Transmigrasi</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C34" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>346039368</v>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
@@ -4031,15 +4517,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M34" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N34" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M34" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" s="10" t="n">
+        <v>346039368</v>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
@@ -4051,15 +4533,11 @@
           <t>Inspektorat Daerah</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>470786500</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -4101,15 +4579,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>470786500</v>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -4122,10 +4596,10 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>293964700</v>
+        <v>523391100</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>2</v>
@@ -4156,10 +4630,10 @@
         </is>
       </c>
       <c r="M36" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>71982350</v>
+        <v>301408750</v>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
@@ -4172,10 +4646,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>471330601</v>
+        <v>835283701</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>6</v>
@@ -4205,15 +4679,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M37" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>363953100</v>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -4222,18 +4692,14 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Kecamatan Arut Utara</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>154997000</v>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
@@ -4275,15 +4741,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="10" t="n">
+        <v>154997000</v>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -4292,14 +4754,14 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
+          <t>Kecamatan Kotawaringin Lama</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>133439000</v>
+        <v>124841500</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -4345,7 +4807,7 @@
         <v>2</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>133439000</v>
+        <v>124841500</v>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -4354,32 +4816,44 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Kecamatan Kumai</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>71700000</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>71700000</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>71700000</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>71700000</v>
+        <v>320725524</v>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
         <is>
@@ -4391,15 +4865,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M40" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N40" s="10" t="n">
+        <v>320725524</v>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
@@ -4408,32 +4878,32 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>239852458</v>
+        <v>137310832</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>239852458</v>
+        <v>71700000</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>65401200</v>
+        <v>71700000</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>65401200</v>
+        <v>71700000</v>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
@@ -4445,15 +4915,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>65610832</v>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
@@ -4462,7 +4928,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
+          <t>Kecamatan Pangkalan Lada</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -4532,32 +4998,32 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Natai Pelingkau</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>302731124</v>
+      </c>
+      <c r="E43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="6" t="n">
-        <v>348491630</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F43" s="6" t="n">
-        <v>153891630</v>
+        <v>239852458</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>53835000</v>
+        <v>65401200</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>53835000</v>
+        <v>65401200</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
@@ -4573,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>194600000</v>
+        <v>62878666</v>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -4582,18 +5048,14 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Puskesmas Arut Selatan</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>305850296</v>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
@@ -4635,15 +5097,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M44" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N44" s="10" t="n">
+        <v>305850296</v>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -4652,32 +5110,44 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Rumah Sakit Kutaringin</t>
+          <t>Puskesmas Arut Utara</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>146817603</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>146817603</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>43541637</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>43541637</v>
+        <v>212926585</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
@@ -4689,15 +5159,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>212926585</v>
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
@@ -4706,32 +5172,44 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+          <t>Puskesmas Ipuh Bangun Jaya</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>50400000</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>50400000</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>49950000</v>
-      </c>
-      <c r="I46" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>49950000</v>
+        <v>154700000</v>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
@@ -4743,15 +5221,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M46" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" s="10" t="n">
+        <v>154700000</v>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
@@ -4760,18 +5234,14 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Satuan Polisi Pamong Praja</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Puskesmas Karang Mulya</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>397980729</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -4813,15 +5283,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>397980729</v>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
@@ -4830,32 +5296,44 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Sekretariat DPRD</t>
+          <t>Puskesmas Kotawaringin Lama</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1435364766</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F48" s="10" t="n">
-        <v>1285364766</v>
-      </c>
-      <c r="G48" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="H48" s="10" t="n">
-        <v>1282534627</v>
-      </c>
-      <c r="I48" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>1226738257</v>
+        <v>50400000</v>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
@@ -4871,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>150000000</v>
+        <v>50400000</v>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
@@ -4880,92 +5358,1114 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
+          <t>Puskesmas Kumai</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>494958640</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>494958640</v>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Kumpai Batu Atas</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>189350000</v>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" s="10" t="n">
+        <v>189350000</v>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Madurejo</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>235342500</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>235342500</v>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Mendawai</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>141393225</v>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" s="10" t="n">
+        <v>141393225</v>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Natai Pelingkau</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>348491630</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>153891630</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>53835000</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>53835000</v>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>194600000</v>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Pandu Sanjaya</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Pangkalan Lada</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>189000000</v>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Riam Durian</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Runtu</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>143150000</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>143150000</v>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Sambi</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>149292000</v>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="10" t="n">
+        <v>149292000</v>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Semanggang</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>275450000</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>275450000</v>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Sungai Rangit</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="10" t="n">
+        <v>66272893</v>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="10" t="n">
+        <v>66272893</v>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Teluk Bogam</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>156525300</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N61" s="6" t="n">
+        <v>156525300</v>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Kutaringin</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>647501699</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>146817603</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>43541637</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>43541637</v>
+      </c>
+      <c r="K62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N62" s="10" t="n">
+        <v>500684096</v>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>3441387498</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>50400000</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>49950000</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>49950000</v>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>3390987498</v>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Satuan Polisi Pamong Praja</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>463002876</v>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N64" s="10" t="n">
+        <v>463002876</v>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Sekretariat DPRD</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>2559430816</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>1285364766</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>1282534627</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>1226738257</v>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N65" s="6" t="n">
+        <v>1274066050</v>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
           <t>Sekretariat Daerah</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>749487047</v>
-      </c>
-      <c r="E49" s="4" t="n">
+      <c r="C66" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="D66" s="10" t="n">
+        <v>2995755132</v>
+      </c>
+      <c r="E66" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F66" s="10" t="n">
         <v>573698247</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G66" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H49" s="6" t="n">
+      <c r="H66" s="10" t="n">
         <v>560374825</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="I66" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J66" s="10" t="n">
         <v>486004825</v>
       </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N49" s="6" t="n">
-        <v>175788800</v>
-      </c>
-    </row>
-    <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="K66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="N66" s="10" t="n">
+        <v>2422056885</v>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
-        <v>442</v>
-      </c>
-      <c r="D50" s="13" t="n">
-        <v>56760118716</v>
-      </c>
-      <c r="E50" s="12" t="n">
+      <c r="C67" s="12" t="n">
+        <v>798</v>
+      </c>
+      <c r="D67" s="13" t="n">
+        <v>94774837904</v>
+      </c>
+      <c r="E67" s="12" t="n">
         <v>417</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="F67" s="13" t="n">
         <v>53479965590</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>417</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="H67" s="13" t="n">
         <v>51736639593.4</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="J50" s="13" t="n">
+      <c r="J67" s="13" t="n">
         <v>24211949095</v>
       </c>
-      <c r="K50" s="12" t="n">
+      <c r="K67" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L50" s="13" t="n">
+      <c r="L67" s="13" t="n">
         <v>764123653</v>
       </c>
-      <c r="M50" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="N50" s="13" t="n">
-        <v>3280153126</v>
+      <c r="M67" s="12" t="n">
+        <v>381</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>41294872314</v>
       </c>
     </row>
   </sheetData>
@@ -4997,7 +6497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5398,15 +6898,11 @@
           <t>Badan Keuangan dan Aset Daerah</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>206878992</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -5448,15 +6944,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>206878992</v>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -5539,10 +7031,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1128517600</v>
+        <v>1344967600</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>1</v>
@@ -5573,10 +7065,10 @@
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>912067600</v>
+        <v>1128517600</v>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -5588,15 +7080,11 @@
           <t>Badan Perencanaan Pembangunan, Riset dan Inovasi Daerah</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>217952667</v>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
@@ -5638,15 +7126,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>217952667</v>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -5658,15 +7142,11 @@
           <t>Dinas Kepemudaan dan Olahraga</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>658884360</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -5708,15 +7188,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>658884360</v>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -5779,10 +7255,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>49112440318</v>
+        <v>50117240767</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>32</v>
@@ -5808,15 +7284,11 @@
       <c r="L17" s="6" t="n">
         <v>1101458974</v>
       </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>1004800449</v>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -5899,10 +7371,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3459514800</v>
+        <v>6129521900</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>4</v>
@@ -5932,15 +7404,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>2670007100</v>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -6007,10 +7475,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>33346991733</v>
+        <v>35948239265</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>42</v>
@@ -6040,15 +7508,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M21" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>2601247532</v>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -6061,10 +7525,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>1086690000</v>
+        <v>1366776000</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>2</v>
@@ -6094,15 +7558,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>280086000</v>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -6114,15 +7574,11 @@
           <t>Dinas Pemberdayaan Masyarakat dan Desa</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>914760000</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -6164,15 +7620,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>914760000</v>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -6184,15 +7636,11 @@
           <t>Dinas Pemberdayaan Perempuan dan Perlindungan Anak, Pengendalian Penduduk dan Keluarga Berencana</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>777000000</v>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
@@ -6234,15 +7682,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>777000000</v>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -6254,15 +7698,11 @@
           <t>Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>205076880</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -6304,15 +7744,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>205076880</v>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -6325,10 +7761,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>1969342000</v>
+        <v>2966457340</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>3</v>
@@ -6359,10 +7795,10 @@
         </is>
       </c>
       <c r="M26" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>1256004000</v>
+        <v>2253119340</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -6375,10 +7811,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>201600000</v>
+        <v>729033456</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>1</v>
@@ -6408,15 +7844,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>527433456</v>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -6429,10 +7861,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1062414494</v>
+        <v>2208956507</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>3</v>
@@ -6463,10 +7895,10 @@
         </is>
       </c>
       <c r="M28" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>229996964</v>
+        <v>1376538977</v>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -6479,10 +7911,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4037584000</v>
+        <v>5338130896</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>4</v>
@@ -6508,15 +7940,11 @@
       <c r="L29" s="6" t="n">
         <v>436796630</v>
       </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>1300546896</v>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -6599,10 +8027,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2620841480</v>
+        <v>3813601480</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>7</v>
@@ -6633,10 +8061,10 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>245000000</v>
+        <v>1437760000</v>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -6649,10 +8077,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>1106740800</v>
+        <v>3639664785</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>2</v>
@@ -6683,10 +8111,10 @@
         </is>
       </c>
       <c r="M32" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>561038400</v>
+        <v>3093962385</v>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -6977,14 +8405,18 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>440899992</v>
+          <t>Kecamatan Arut Utara</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
@@ -7026,11 +8458,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" s="10" t="n">
-        <v>440899992</v>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -7039,18 +8475,14 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Kecamatan Kotawaringin Lama</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>440899992</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -7092,15 +8524,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>440899992</v>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -7109,7 +8537,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Kecamatan Kumai</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -7179,7 +8607,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -7249,7 +8677,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
+          <t>Kecamatan Pangkalan Lada</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -7319,18 +8747,14 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Laboratorium Kesehatan Daerah</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>1937370950</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -7372,15 +8796,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>1937370950</v>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -7389,18 +8809,14 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Puskesmas Arut Selatan</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>1032445697</v>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
@@ -7442,15 +8858,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="10" t="n">
+        <v>1032445697</v>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -7459,18 +8871,14 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Rumah Sakit Kutaringin</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Puskesmas Arut Utara</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>456516000</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -7512,15 +8920,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>456516000</v>
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
@@ -7529,38 +8933,58 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>7812519000</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>7812519000</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>2779934202</v>
-      </c>
-      <c r="I46" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>2779934202</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="10" t="n">
-        <v>64551162</v>
+          <t>Puskesmas Ipuh Bangun Jaya</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
@@ -7579,7 +9003,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Satuan Polisi Pamong Praja</t>
+          <t>Puskesmas Karang Mulya</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -7649,32 +9073,48 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Sekretariat DPRD</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="10" t="n">
-        <v>218268000</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="10" t="n">
-        <v>218268000</v>
-      </c>
-      <c r="G48" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="10" t="n">
-        <v>185076000</v>
-      </c>
-      <c r="I48" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>185076000</v>
+          <t>Puskesmas Kotawaringin Lama</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
@@ -7703,96 +9143,1222 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
+          <t>Puskesmas Kumai</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>223700000</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>223700000</v>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Kumpai Batu Atas</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Madurejo</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Mendawai</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Natai Pelingkau</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Pandu Sanjaya</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Pangkalan Lada</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Riam Durian</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Runtu</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Sambi</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Semanggang</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Sungai Rangit</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Teluk Bogam</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Kutaringin</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>15827645837</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>7812519000</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>2779934202</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>2779934202</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L63" s="6" t="n">
+        <v>64551162</v>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>8015126837</v>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Satuan Polisi Pamong Praja</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>211404000</v>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="10" t="n">
+        <v>211404000</v>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Sekretariat DPRD</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>5031291001</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>218268000</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>185076000</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>185076000</v>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N65" s="6" t="n">
+        <v>4813023001</v>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
           <t>Sekretariat Daerah</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C66" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D66" s="10" t="n">
+        <v>7626623356</v>
+      </c>
+      <c r="E66" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="F66" s="10" t="n">
         <v>2944207800</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="G66" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="6" t="n">
-        <v>2944207800</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H49" s="6" t="n">
+      <c r="H66" s="10" t="n">
         <v>2058441500</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="I66" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J66" s="10" t="n">
         <v>2058441500</v>
       </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="K66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="N66" s="10" t="n">
+        <v>4682415556</v>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="D50" s="13" t="n">
-        <v>117525967542</v>
-      </c>
-      <c r="E50" s="12" t="n">
+      <c r="C67" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="D67" s="13" t="n">
+        <v>156348435253</v>
+      </c>
+      <c r="E67" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="F67" s="13" t="n">
         <v>112850154586</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="H67" s="13" t="n">
         <v>55094743286</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="J50" s="13" t="n">
+      <c r="J67" s="13" t="n">
         <v>53004449286</v>
       </c>
-      <c r="K50" s="12" t="n">
+      <c r="K67" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L50" s="13" t="n">
+      <c r="L67" s="13" t="n">
         <v>2094471498</v>
       </c>
-      <c r="M50" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="N50" s="13" t="n">
-        <v>4675812956</v>
+      <c r="M67" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>43498280667</v>
       </c>
     </row>
   </sheetData>
@@ -7824,7 +10390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9298,10 +11864,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>5040000000</v>
+        <v>8328788319</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>1</v>
@@ -9331,15 +11897,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>3288788319</v>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -9545,15 +12107,11 @@
           <t>Dinas Pertanian</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>2509875000</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -9595,15 +12153,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>2509875000</v>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -10032,7 +12586,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
+          <t>Kecamatan Arut Utara</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -10102,7 +12656,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
+          <t>Kecamatan Kotawaringin Lama</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -10172,7 +12726,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Kecamatan Kumai</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -10242,7 +12796,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -10312,7 +12866,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
+          <t>Kecamatan Pangkalan Lada</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -10382,7 +12936,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Natai Pelingkau</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -10452,7 +13006,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Riam Durian</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -10522,7 +13076,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Rumah Sakit Kutaringin</t>
+          <t>Puskesmas Arut Utara</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -10592,32 +13146,48 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>73360000000</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>73360000000</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>8116023274</v>
-      </c>
-      <c r="I46" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>8116023274</v>
+          <t>Puskesmas Ipuh Bangun Jaya</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
@@ -10646,7 +13216,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Satuan Polisi Pamong Praja</t>
+          <t>Puskesmas Karang Mulya</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -10716,7 +13286,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Sekretariat DPRD</t>
+          <t>Puskesmas Kotawaringin Lama</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -10786,116 +13356,1286 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
+          <t>Puskesmas Kumai</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Kumpai Batu Atas</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Madurejo</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Mendawai</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Natai Pelingkau</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Pandu Sanjaya</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Pangkalan Lada</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Riam Durian</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Runtu</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Sambi</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Semanggang</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Puskesmas Sungai Rangit</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Puskesmas Teluk Bogam</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Kutaringin</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>135106211738</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>73360000000</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>8116023274</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>8116023274</v>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>61746211738</v>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Satuan Polisi Pamong Praja</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Sekretariat DPRD</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
           <t>Sekretariat Daerah</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="D50" s="13" t="n">
-        <v>187157560800</v>
-      </c>
-      <c r="E50" s="12" t="n">
+      <c r="C67" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D67" s="13" t="n">
+        <v>254702435857</v>
+      </c>
+      <c r="E67" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="F67" s="13" t="n">
         <v>137115370800</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="H67" s="13" t="n">
         <v>71014601008.97</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J50" s="13" t="n">
+      <c r="J67" s="13" t="n">
         <v>71014601008.97</v>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="N50" s="13" t="n">
-        <v>50042190000</v>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>117587065057</v>
       </c>
     </row>
   </sheetData>
